--- a/AAII_Financials/Quarterly/PRNDY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PRNDY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="375" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="92">
   <si>
     <t>PRNDY</t>
   </si>
@@ -656,83 +656,91 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -778,8 +786,14 @@
       <c r="Q8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -825,8 +839,14 @@
       <c r="Q9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -872,8 +892,14 @@
       <c r="Q10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -891,8 +917,10 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -938,8 +966,14 @@
       <c r="Q12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -985,8 +1019,14 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1032,8 +1072,14 @@
       <c r="Q14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1079,8 +1125,14 @@
       <c r="Q15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1095,8 +1147,10 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1142,8 +1196,14 @@
       <c r="Q17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1189,8 +1249,14 @@
       <c r="Q18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1208,8 +1274,10 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1255,8 +1323,14 @@
       <c r="Q20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1302,8 +1376,14 @@
       <c r="Q21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1349,8 +1429,14 @@
       <c r="Q22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1396,8 +1482,14 @@
       <c r="Q23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1443,8 +1535,14 @@
       <c r="Q24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1490,8 +1588,14 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1537,8 +1641,14 @@
       <c r="Q26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1584,8 +1694,14 @@
       <c r="Q27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1631,8 +1747,14 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1678,8 +1800,14 @@
       <c r="Q29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1725,8 +1853,14 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1772,8 +1906,14 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1819,8 +1959,14 @@
       <c r="Q32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1866,8 +2012,14 @@
       <c r="Q33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1913,8 +2065,14 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1960,60 +2118,72 @@
       <c r="Q35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2031,8 +2201,10 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2050,55 +2222,63 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2276900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>2297900</v>
+      </c>
+      <c r="F41" s="3">
         <v>2815500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>2813600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>2148000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>1976900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>1983600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>2137000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>2874700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>2894600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>1811700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>1734800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>1756600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>1748200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>1919400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1761100</v>
       </c>
     </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2144,337 +2324,385 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2008500</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2027000</v>
+      </c>
+      <c r="F43" s="3">
         <v>2463300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>2461600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2170300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1997400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2638000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2841800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2089400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2103800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>3133600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>3000600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2310000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>2299000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3065100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2812300</v>
       </c>
     </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>9676700</v>
+      </c>
+      <c r="E44" s="3">
+        <v>9765900</v>
+      </c>
+      <c r="F44" s="3">
         <v>9828600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>9821700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>9886100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>9098600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>8720400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>9394400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>8845000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>8906000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>9121300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>8734100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>8847200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>8804900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>8087000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>7420100</v>
       </c>
     </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E45" s="3">
+        <v>79600</v>
+      </c>
+      <c r="F45" s="3">
         <v>237200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>237000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>162100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>149200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>468000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>504100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>491800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>495200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>143700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>137600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>63300</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>63000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>66300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>60800</v>
       </c>
     </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>14170000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>14300700</v>
+      </c>
+      <c r="F46" s="3">
         <v>15452600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>15441700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>14513200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>13357100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>13919700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>14995500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>14421900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>14521500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>14351700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>13742600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>13110300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>13047600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>13239300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>12147500</v>
       </c>
     </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>892300</v>
+      </c>
+      <c r="E47" s="3">
+        <v>900500</v>
+      </c>
+      <c r="F47" s="3">
         <v>807800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>807200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>735200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>676600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>671900</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>723800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>604300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>608500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1054500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1009700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>519700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>517200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>42700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>39200</v>
       </c>
     </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4783500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>4827600</v>
+      </c>
+      <c r="F48" s="3">
         <v>4850300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>4846900</v>
       </c>
-      <c r="F48" s="3">
-        <v>4927800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>4535200</v>
-      </c>
       <c r="H48" s="3">
+        <v>4939500</v>
+      </c>
+      <c r="I48" s="3">
+        <v>4546000</v>
+      </c>
+      <c r="J48" s="3">
         <v>4416600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>4758000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>4252700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>4282000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>4493200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>4302500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>4245600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>4225300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>3862300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>3543800</v>
       </c>
     </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>20564400</v>
+      </c>
+      <c r="E49" s="3">
+        <v>20754100</v>
+      </c>
+      <c r="F49" s="3">
         <v>20784300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>20769700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>21046400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>19369900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>20012400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>21559200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>20400700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>20541600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>20863300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>19977800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>20742400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>20643200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>19564000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>17950600</v>
       </c>
     </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2520,8 +2748,14 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2567,55 +2801,67 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>183900</v>
+      </c>
+      <c r="E52" s="3">
+        <v>185600</v>
+      </c>
+      <c r="F52" s="3">
         <v>290000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>289800</v>
       </c>
-      <c r="F52" s="3">
-        <v>304200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>279900</v>
-      </c>
       <c r="H52" s="3">
+        <v>292400</v>
+      </c>
+      <c r="I52" s="3">
+        <v>269100</v>
+      </c>
+      <c r="J52" s="3">
         <v>226700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>244300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>263600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>265400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>8800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>8500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>268600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>267300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>812200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>745200</v>
       </c>
     </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2661,55 +2907,67 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>42610500</v>
+      </c>
+      <c r="E54" s="3">
+        <v>43003600</v>
+      </c>
+      <c r="F54" s="3">
         <v>44236200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>44205100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>43546700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>40077800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>41199900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>44384300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>41985400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>42275300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>42817500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>41000200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>41131000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>40934400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>39409000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>36159100</v>
       </c>
     </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2727,8 +2985,10 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2746,290 +3006,328 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2945300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2972400</v>
+      </c>
+      <c r="F57" s="3">
         <v>2904800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>2902700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>3183800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>2930200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>2823300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>3041500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>3139400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>3161100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>3391200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>3247200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>3778400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>3760300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>3443400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>3159400</v>
       </c>
     </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>666100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>672200</v>
+      </c>
+      <c r="F58" s="3">
         <v>1967800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1966400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>2130400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1960700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>2478500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>2670100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>2391500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>2408000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>2406300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>2304200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1784900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>1776400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>1317700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>1209100</v>
       </c>
     </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1160700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>1171500</v>
+      </c>
+      <c r="F59" s="3">
         <v>724400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>723900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>1296500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>1193300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>803400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>865500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>1310400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>1319500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>693000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>663600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>1096100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>1090800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>677600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>621700</v>
       </c>
     </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5727200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>5780000</v>
+      </c>
+      <c r="F60" s="3">
         <v>6592700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>6588100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>7574900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6971500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7045200</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7589800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>7759600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>7813100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7503000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>7184600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>7571000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>7534800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>6373800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>5848200</v>
       </c>
     </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>13817000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>13944400</v>
+      </c>
+      <c r="F61" s="3">
         <v>14002600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>13992700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>12658800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>11650500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>11955700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>12879800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>12216900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>12301200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>11995100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>11486000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>11188900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>11135400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>11062300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>10150000</v>
       </c>
     </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>353000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>356300</v>
+      </c>
+      <c r="F62" s="3">
         <v>333500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>333200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>348800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>321000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>328200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>353600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>336400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>338800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>332700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>318600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>321000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>319400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>314200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>288300</v>
       </c>
     </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3075,8 +3373,14 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3122,8 +3426,14 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3169,55 +3479,67 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>23714200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>23932900</v>
+      </c>
+      <c r="F66" s="3">
         <v>24829200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>24811700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>24490900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>22540000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>22945400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>24718900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>23988000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>24153600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>23795700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>22785800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>22883200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>22773800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>21499400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>19726400</v>
       </c>
     </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3235,8 +3557,10 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3282,8 +3606,14 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3329,8 +3659,14 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3376,8 +3712,14 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3423,55 +3765,67 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1374400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>1387100</v>
+      </c>
+      <c r="F72" s="3">
         <v>1144800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>1144000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>1909600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>1757500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1232000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1327200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>1581500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>1592400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>1734300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>1660700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>2469400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>2457600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1916200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1758200</v>
       </c>
     </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3517,8 +3871,14 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3564,8 +3924,14 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3611,55 +3977,67 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17708200</v>
+      </c>
+      <c r="E76" s="3">
+        <v>17871600</v>
+      </c>
+      <c r="F76" s="3">
         <v>18169500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>18156800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>17864900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>16441900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>17127000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>18450800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>16874500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>16991000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>17898800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>17139100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>17158300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>17076300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>17543000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>16096300</v>
       </c>
     </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3705,60 +4083,72 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3804,8 +4194,14 @@
       <c r="Q81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3823,55 +4219,63 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>72800</v>
+      </c>
+      <c r="E83" s="3">
+        <v>67000</v>
+      </c>
+      <c r="F83" s="3">
         <v>109200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>117700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>120000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>120800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>119900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>114800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>116300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>115700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>109000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>100000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>100400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>106600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>107500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>109500</v>
       </c>
     </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3917,8 +4321,14 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3964,8 +4374,14 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4011,8 +4427,14 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4058,8 +4480,14 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4105,55 +4533,67 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>502700</v>
+      </c>
+      <c r="E89" s="3">
+        <v>507300</v>
+      </c>
+      <c r="F89" s="3">
         <v>410400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>410100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>577200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>531200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>416700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>448900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>555000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>558900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>381900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>365700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>496200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>493800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>600600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>551100</v>
       </c>
     </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4171,55 +4611,63 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-97100</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-129700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-129600</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-174400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-160500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-191500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-206300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-203600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-205000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-217200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-208000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-236900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-235800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-143200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-131400</v>
       </c>
     </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4265,8 +4713,14 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4312,55 +4766,67 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-51400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-51900</v>
+      </c>
+      <c r="F94" s="3">
         <v>48100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>48100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-8800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-8100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-261900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-282200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-143000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-144000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-226000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-216400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-385400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-383500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-547700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-502500</v>
       </c>
     </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4378,55 +4844,63 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F96" s="3">
         <v>702700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>702200</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>4100</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>3800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>618100</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>665800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>4800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>4900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>662700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>634500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>3800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>3800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>569100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>522200</v>
       </c>
     </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4472,8 +4946,14 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4519,8 +4999,14 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4566,145 +5052,169 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-698000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-704500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-110400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-110300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-683500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-629100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-637700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-687000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>80900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>81500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-199000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-190500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-161000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-160300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-439200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-403000</v>
       </c>
     </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>63400</v>
+      </c>
+      <c r="E101" s="3">
+        <v>58400</v>
+      </c>
+      <c r="F101" s="3">
         <v>86400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>93100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>67000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>67400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>59100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>56600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-51900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-51600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-4300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-3900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>4700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>5000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>18800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>19100</v>
       </c>
     </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-231900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-234100</v>
+      </c>
+      <c r="F102" s="3">
         <v>334600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>334400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-51700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-47600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-396500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-427200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>559800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>563700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>16000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>15300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-102100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-101600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>-390600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-358400</v>
       </c>
     </row>
